--- a/JsonConverter/ExcelFiles/RobbyDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/RobbyDialogueGroup.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25545" windowHeight="7755"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,73 +14,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <x:si>
-    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011</x:t>
+    <x:t>dialogue_title_1_1_001,dialogue_detail1_1_001</x:t>
   </x:si>
   <x:si>
-    <x:t>질의 독백</x:t>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_002,dialogue_detail1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_000,dialogue_detail1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_1_1</x:t>
   </x:si>
   <x:si>
     <x:t>Comment</x:t>
   </x:si>
   <x:si>
-    <x:t>튜토리얼 시작</x:t>
+    <x:t>dialogue_group_1_3</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_tutorial_1_3_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">dialogue_tutorial_1_1_009,dialogue_tutorial_1_1_010,dialogue_tutorial_1_1_011,dialogue_tutorial_1_1_012,dialogue_tutorial_1_1_013,dialogue_tutorial_1_1_014,dialogue_tutorial_1_1_015,dialogue_tutorial_1_1_016,dialogue_tutorial_1_1_017,dialogue_tutorial_1_1_018,dialogue_tutorial_1_1_019,dialogue_tutorial_1_1_020,dialogue_tutorial_1_1_021,dialogue_tutorial_1_1_022,dialogue_tutorial_1_1_023,dialogue_tutorial_1_1_024,dialogue_tutorial_1_1_025,dialogue_tutorial_1_1_026
-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueIdList</x:t>
+    <x:t>dialogue_group_1_2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -969,42 +941,40 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
+      <x:c r="B4" s="4"/>
       <x:c r="C4" s="13" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1021,13 +991,11 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B5" s="5"/>
       <x:c r="C5" s="14" t="s">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1044,13 +1012,11 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="B6" s="5"/>
       <x:c r="C6" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1066,15 +1032,9 @@
       <x:c r="O6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="12" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="A7" s="12"/>
+      <x:c r="B7" s="4"/>
+      <x:c r="C7" s="4"/>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
       <x:c r="F7" s="3"/>
@@ -1089,15 +1049,9 @@
       <x:c r="O7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="12" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="A8" s="12"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
       <x:c r="D8" s="3"/>
       <x:c r="E8" s="3"/>
       <x:c r="F8" s="3"/>
